--- a/out/_smoke_export.xlsx
+++ b/out/_smoke_export.xlsx
@@ -8,26 +8,26 @@
   </bookViews>
   <sheets>
     <sheet name="汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="create_normal_20260924_15384" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="create_destroy_20260924_1538" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="create_normal_20260924_15321" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="create_destroy_20260924_1532" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="account_normal_20260924_1528" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="create_normal_20260924_15095" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="create_destroy_20260924_1509" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="create_normal_20260924_15074" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="create_destroy_20260924_1507" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="create_normal_20260924_15010" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="create_destroy_20260924_1500" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="create_normal_20260924_15003" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="create_destroy_20260924_15001" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="e2e" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="137真平台-pwdUpdate加密" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="137真平台-remove" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="137真平台-account" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="137真平台-pwdUpdate" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="137真平台-modify" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="137真平台-create" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="create_normal_20260928_09452" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="create_destroy_20260928_0945" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="remove_normal_20260928_09363" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="pwdUpdate_normal_20260928_09" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="modify_normal_20260928_09360" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="create_normal_20260928_09353" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="account_normal_20260928_0935" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="account_normal_20260928_0928" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="create_normal_20260924_15395" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="create_destroy_20260924_1539" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="create_normal_20260924_15384" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="create_destroy_20260924_1538" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="create_normal_20260924_15321" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="create_destroy_20260924_1532" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="account_normal_20260924_1528" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="create_normal_20260924_15095" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="create_destroy_20260924_1509" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="create_normal_20260924_15074" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="create_destroy_20260924_1507" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="create_normal_20260924_15010" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -473,16 +473,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>create_normal_20260924_153848</t>
+          <t>create_normal_20260928_094522</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09-24 15:38:49</t>
+          <t>09-28 09:45:23</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="D2" t="n">
         <v>30</v>
@@ -494,79 +494,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_153836</t>
+          <t>create_destroy_20260928_094514</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09-24 15:38:37</t>
+          <t>09-28 09:45:15</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.837</v>
+        <v>0.845</v>
       </c>
       <c r="D3" t="n">
         <v>50</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>create_normal_20260924_153218</t>
+          <t>remove_normal_20260928_093634</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09-24 15:32:18</t>
+          <t>09-28 09:36:35</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.832</v>
+        <v>0.819</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_153206</t>
+          <t>pwdUpdate_normal_20260928_093620</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09-24 15:32:06</t>
+          <t>09-28 09:36:21</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.838</v>
+        <v>0.826</v>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>account_normal_20260924_152832</t>
+          <t>modify_normal_20260928_093605</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09-24 15:28:33</t>
+          <t>09-28 09:36:06</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -578,205 +578,205 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>create_normal_20260924_150953</t>
+          <t>create_normal_20260928_093535</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09-24 15:09:54</t>
+          <t>09-28 09:35:36</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.832</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_150941</t>
+          <t>account_normal_20260928_093500</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09-24 15:09:42</t>
+          <t>09-28 09:35:00</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.835</v>
+        <v>0.832</v>
       </c>
       <c r="D8" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>create_normal_20260924_150746</t>
+          <t>account_normal_20260928_092824</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09-24 15:07:47</t>
+          <t>09-28 09:28:25</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_150734</t>
+          <t>create_normal_20260924_153954</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09-24 15:07:35</t>
+          <t>09-24 15:39:55</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.847</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>create_normal_20260924_150107</t>
+          <t>create_destroy_20260924_153942</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09-24 15:01:08</t>
+          <t>09-24 15:39:43</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.857</v>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_150056</t>
+          <t>create_normal_20260924_153848</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09-24 15:00:57</t>
+          <t>09-24 15:38:49</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.833</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E12" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>create_normal_20260924_150034</t>
+          <t>create_destroy_20260924_153836</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09-24 15:00:35</t>
+          <t>09-24 15:38:37</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.837</v>
       </c>
       <c r="D13" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_150022</t>
+          <t>create_normal_20260924_153218</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09-24 15:00:23</t>
+          <t>09-24 15:32:18</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.836</v>
+        <v>0.832</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>e2e</t>
+          <t>create_destroy_20260924_153206</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09-24 14:59:55</t>
+          <t>09-24 15:32:06</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.823</v>
+        <v>0.838</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>137真平台-pwdUpdate加密</t>
+          <t>account_normal_20260924_152832</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09-24 14:58:17</t>
+          <t>09-24 15:28:33</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -788,331 +788,331 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>137真平台-remove</t>
+          <t>create_normal_20260924_150953</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09-24 14:57:22</t>
+          <t>09-24 15:09:54</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.828</v>
+        <v>0.832</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>137真平台-account</t>
+          <t>create_destroy_20260924_150941</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09-24 14:57:15</t>
+          <t>09-24 15:09:42</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.805</v>
+        <v>0.835</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>137真平台-pwdUpdate</t>
+          <t>create_normal_20260924_150746</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09-24 14:56:47</t>
+          <t>09-24 15:07:47</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.931</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>137真平台-modify</t>
+          <t>create_destroy_20260924_150734</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09-24 14:56:35</t>
+          <t>09-24 15:07:35</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.806</v>
+        <v>0.847</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>137真平台-create</t>
+          <t>create_normal_20260924_150107</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09-24 14:56:11</t>
+          <t>09-24 15:01:08</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.826</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>create_normal_20260924_144400</t>
+          <t>create_destroy_20260924_150056</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09-24 14:44:01</t>
+          <t>09-24 15:00:57</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.819</v>
+        <v>0.833</v>
       </c>
       <c r="D22" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E22" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_144348</t>
+          <t>create_normal_20260924_150034</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09-24 14:43:49</t>
+          <t>09-24 15:00:35</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.855</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E23" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>create_normal_20260924_144210</t>
+          <t>create_destroy_20260924_150022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09-24 14:42:11</t>
+          <t>09-24 15:00:23</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.82</v>
+        <v>0.836</v>
       </c>
       <c r="D24" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E24" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_144159</t>
+          <t>e2e</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>09-24 14:42:00</t>
+          <t>09-24 14:59:55</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.851</v>
+        <v>0.823</v>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>create_normal_20260924_143447</t>
+          <t>137真平台-pwdUpdate加密</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>09-24 14:34:47</t>
+          <t>09-24 14:58:17</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_143435</t>
+          <t>137真平台-remove</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>09-24 14:34:36</t>
+          <t>09-24 14:57:22</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.852</v>
+        <v>0.828</v>
       </c>
       <c r="D27" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>create_normal_20260924_142426</t>
+          <t>137真平台-account</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>09-24 14:24:27</t>
+          <t>09-24 14:57:15</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.824</v>
+        <v>0.805</v>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_142415</t>
+          <t>137真平台-pwdUpdate</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>09-24 14:24:16</t>
+          <t>09-24 14:56:47</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.838</v>
+        <v>2.931</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>create_normal_20260924_141949</t>
+          <t>137真平台-modify</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>09-24 14:19:50</t>
+          <t>09-24 14:56:35</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.83</v>
+        <v>0.806</v>
       </c>
       <c r="D30" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_141937</t>
+          <t>137真平台-create</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>09-24 14:19:38</t>
+          <t>09-24 14:56:11</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.842</v>
+        <v>0.826</v>
       </c>
       <c r="D31" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>create_normal_20260924_141739</t>
+          <t>create_normal_20260924_144400</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>09-24 14:17:40</t>
+          <t>09-24 14:44:01</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.842</v>
+        <v>0.819</v>
       </c>
       <c r="D32" t="n">
         <v>30</v>
@@ -1124,16 +1124,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_141728</t>
+          <t>create_destroy_20260924_144348</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>09-24 14:17:29</t>
+          <t>09-24 14:43:49</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.856</v>
+        <v>0.855</v>
       </c>
       <c r="D33" t="n">
         <v>50</v>
@@ -1145,16 +1145,16 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>create_normal_20260924_134011</t>
+          <t>create_normal_20260924_144210</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>09-24 13:40:12</t>
+          <t>09-24 14:42:11</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.857</v>
+        <v>0.82</v>
       </c>
       <c r="D34" t="n">
         <v>30</v>
@@ -1166,16 +1166,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_134003</t>
+          <t>create_destroy_20260924_144159</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>09-24 13:40:03</t>
+          <t>09-24 14:42:00</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.877</v>
+        <v>0.851</v>
       </c>
       <c r="D35" t="n">
         <v>50</v>
@@ -1187,16 +1187,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>create_normal_20260924_133830</t>
+          <t>create_normal_20260924_143447</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>09-24 13:38:31</t>
+          <t>09-24 14:34:47</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.838</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="D36" t="n">
         <v>30</v>
@@ -1208,37 +1208,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_133822</t>
+          <t>create_destroy_20260924_143435</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>09-24 13:38:23</t>
+          <t>09-24 14:34:36</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.857</v>
+        <v>0.852</v>
       </c>
       <c r="D37" t="n">
         <v>50</v>
       </c>
       <c r="E37" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>create_normal_20260924_132515</t>
+          <t>create_normal_20260924_142426</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>09-24 13:25:16</t>
+          <t>09-24 14:24:27</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.858</v>
+        <v>0.824</v>
       </c>
       <c r="D38" t="n">
         <v>30</v>
@@ -1250,16 +1250,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_132507</t>
+          <t>create_destroy_20260924_142415</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>09-24 13:25:08</t>
+          <t>09-24 14:24:16</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.867</v>
+        <v>0.838</v>
       </c>
       <c r="D39" t="n">
         <v>50</v>
@@ -1271,16 +1271,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>create_normal_20260924_132347</t>
+          <t>create_normal_20260924_141949</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>09-24 13:23:48</t>
+          <t>09-24 14:19:50</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.845</v>
+        <v>0.83</v>
       </c>
       <c r="D40" t="n">
         <v>30</v>
@@ -1292,16 +1292,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_132339</t>
+          <t>create_destroy_20260924_141937</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>09-24 13:23:40</t>
+          <t>09-24 14:19:38</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.865</v>
+        <v>0.842</v>
       </c>
       <c r="D41" t="n">
         <v>50</v>
@@ -1313,16 +1313,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>create_normal_20260924_131457</t>
+          <t>create_normal_20260924_141739</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>09-24 13:14:58</t>
+          <t>09-24 14:17:40</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.819</v>
+        <v>0.842</v>
       </c>
       <c r="D42" t="n">
         <v>30</v>
@@ -1334,16 +1334,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_131449</t>
+          <t>create_destroy_20260924_141728</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>09-24 13:14:50</t>
+          <t>09-24 14:17:29</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.858</v>
+        <v>0.856</v>
       </c>
       <c r="D43" t="n">
         <v>50</v>
@@ -1355,16 +1355,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>create_normal_20260924_130616</t>
+          <t>create_normal_20260924_134011</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>09-24 13:06:17</t>
+          <t>09-24 13:40:12</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.824</v>
+        <v>0.857</v>
       </c>
       <c r="D44" t="n">
         <v>30</v>
@@ -1376,16 +1376,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_130608</t>
+          <t>create_destroy_20260924_134003</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>09-24 13:06:09</t>
+          <t>09-24 13:40:03</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.871</v>
+        <v>0.877</v>
       </c>
       <c r="D45" t="n">
         <v>50</v>
@@ -1397,16 +1397,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>create_normal_20260924_112134</t>
+          <t>create_normal_20260924_133830</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>09-24 11:21:34</t>
+          <t>09-24 13:38:31</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.829</v>
+        <v>0.838</v>
       </c>
       <c r="D46" t="n">
         <v>30</v>
@@ -1418,16 +1418,16 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_112125</t>
+          <t>create_destroy_20260924_133822</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>09-24 11:21:26</t>
+          <t>09-24 13:38:23</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.858</v>
+        <v>0.857</v>
       </c>
       <c r="D47" t="n">
         <v>50</v>
@@ -1439,16 +1439,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>create_normal_20260924_112013</t>
+          <t>create_normal_20260924_132515</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>09-24 11:20:14</t>
+          <t>09-24 13:25:16</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.819</v>
+        <v>0.858</v>
       </c>
       <c r="D48" t="n">
         <v>30</v>
@@ -1460,16 +1460,16 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_112005</t>
+          <t>create_destroy_20260924_132507</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>09-24 11:20:06</t>
+          <t>09-24 13:25:08</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.869</v>
+        <v>0.867</v>
       </c>
       <c r="D49" t="n">
         <v>50</v>
@@ -1481,63 +1481,273 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>create_destroy_20260924_111908</t>
+          <t>create_normal_20260924_132347</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>09-24 11:19:09</t>
+          <t>09-24 13:23:48</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.879</v>
+        <v>0.845</v>
       </c>
       <c r="D50" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E50" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>create_normal_20260924_111820</t>
+          <t>create_destroy_20260924_132339</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>09-24 11:18:21</t>
+          <t>09-24 13:23:40</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.824</v>
+        <v>0.865</v>
       </c>
       <c r="D51" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E51" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>create_normal_20260924_131457</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>09-24 13:14:58</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="D52" t="n">
+        <v>30</v>
+      </c>
+      <c r="E52" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>create_destroy_20260924_131449</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>09-24 13:14:50</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="D53" t="n">
+        <v>50</v>
+      </c>
+      <c r="E53" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>create_normal_20260924_130616</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>09-24 13:06:17</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="D54" t="n">
+        <v>30</v>
+      </c>
+      <c r="E54" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>create_destroy_20260924_130608</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>09-24 13:06:09</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="D55" t="n">
+        <v>50</v>
+      </c>
+      <c r="E55" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>create_normal_20260924_112134</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>09-24 11:21:34</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="D56" t="n">
+        <v>30</v>
+      </c>
+      <c r="E56" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>create_destroy_20260924_112125</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>09-24 11:21:26</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="D57" t="n">
+        <v>50</v>
+      </c>
+      <c r="E57" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>create_normal_20260924_112013</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>09-24 11:20:14</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="D58" t="n">
+        <v>30</v>
+      </c>
+      <c r="E58" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>create_destroy_20260924_112005</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>09-24 11:20:06</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="D59" t="n">
+        <v>50</v>
+      </c>
+      <c r="E59" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>create_destroy_20260924_111908</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>09-24 11:19:09</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="D60" t="n">
+        <v>50</v>
+      </c>
+      <c r="E60" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>create_normal_20260924_111820</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>09-24 11:18:21</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="D61" t="n">
+        <v>30</v>
+      </c>
+      <c r="E61" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>quickstart</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>09-24 11:04:22</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C62" t="n">
         <v>1.615</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D62" t="n">
         <v>2000</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E62" t="n">
         <v>2020</v>
       </c>
     </row>
@@ -1577,10 +1787,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1619,10 +1829,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1661,10 +1871,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>69</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1703,10 +1913,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1745,10 +1955,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1787,10 +1997,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1871,10 +2081,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1913,10 +2123,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1955,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2039,10 +2249,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2081,10 +2291,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2165,10 +2375,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2207,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2291,10 +2501,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2333,10 +2543,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2375,10 +2585,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
